--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,676 +808,694 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9987,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9524,0.0004,0.0001,0.0467</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.0006,0.9992</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9860,0.0005,0.0001,0.0091</t>
+  </si>
+  <si>
+    <t>0.0169,0.0002,0.0002,0.9927</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9661,0.0005,0.0207,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0009,0.9954,0.0007</t>
+  </si>
+  <si>
+    <t>0.4484,0.0001,0.7918,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0016,0.9975,0.0002</t>
+  </si>
+  <si>
+    <t>0.9613,0.0002,0.0237,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9980,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.3950,0.5456,0.0622,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9125,0.0012,0.0680,0.0008</t>
+  </si>
+  <si>
+    <t>0.0418,0.0007,0.9455,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0038,0.0001,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.5287,0.0002,0.5434,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9922,0.0058,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9982,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0023,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.3127,0.0083,0.5889,0.0005</t>
+  </si>
+  <si>
+    <t>0.6381,0.3986,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.9975,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.7862,0.3904,0.0043</t>
+  </si>
+  <si>
+    <t>0.0343,0.0208,0.8912,0.0019</t>
+  </si>
+  <si>
+    <t>0.0018,0.0009,0.9949,0.0003</t>
+  </si>
+  <si>
+    <t>0.9374,0.0001,0.0943,0.0000</t>
+  </si>
+  <si>
+    <t>0.0079,0.3345,0.9689,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0038,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9899,0.0003,0.9270</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1049,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0161,0.0007,0.9811,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0243,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0045,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.8944,0.0692,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0261,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0023,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9806,0.8115,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0031,0.9952,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9973,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9835,0.0008,0.0095,0.0001</t>
+  </si>
+  <si>
+    <t>0.9291,0.0027,0.0533,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.0018,0.9976,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9954,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9955,0.7912,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0049,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.1180,0.0000</t>
+  </si>
+  <si>
+    <t>0.0055,0.0000,0.0175,0.9836</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0012,0.9991</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.9982,0.1789,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9753,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9873,0.9777,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7345,0.9734,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9574,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0696,0.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0094,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0060,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0075,0.0014,0.9936,0.0003</t>
+  </si>
+  <si>
+    <t>0.0073,0.0009,0.9954,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0037,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.9961,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9977,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2330,0.8042,0.0116,0.0007</t>
+  </si>
+  <si>
+    <t>0.0888,0.0922,0.4485,0.0021</t>
+  </si>
+  <si>
+    <t>0.8977,0.0561,0.0049,0.0001</t>
+  </si>
+  <si>
+    <t>0.1438,0.0197,0.4707,0.0240</t>
+  </si>
+  <si>
+    <t>0.0092,0.0044,0.9832,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.9387,0.0029,0.3265</t>
+  </si>
+  <si>
+    <t>0.0006,0.9986,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9810,0.9472,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9977,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.3339,0.6997,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.2087,0.8195,0.0047,0.0010</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6391,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8910,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0038,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0050,0.0009,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.9903,0.0002,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.8655,0.0008,0.0955,0.0006</t>
+  </si>
+  <si>
+    <t>0.0978,0.0001,0.9570,0.0001</t>
+  </si>
+  <si>
+    <t>0.6443,0.0013,0.4249,0.0007</t>
+  </si>
+  <si>
+    <t>0.7554,0.0012,0.0002,0.3107</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9679,0.0000</t>
+  </si>
+  <si>
+    <t>0.4767,0.5215,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0438,0.9633,0.0020,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
+    <t>0.0960,0.0001,0.0112,0.8952</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0104,0.9943,0.0010</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.1810,0.5222,0.0511,0.0034</t>
+  </si>
+  <si>
+    <t>0.9971,0.0013,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9723,0.0092,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.0213,0.9694,0.0013,0.0036</t>
+  </si>
+  <si>
+    <t>0.9644,0.0323,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.4237,0.6840,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.6960,0.4045,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.4355,0.7086,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9814,0.0177,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9967,0.0024,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9889,0.0070,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0159,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9781,0.0110,0.0062,0.0031</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0048,0.9976,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0040,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0059,0.0000,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0026,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0360,0.0008,0.9619,0.0015</t>
+  </si>
+  <si>
+    <t>0.0133,0.0003,0.9908,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0010,0.9981,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.0003,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0094,0.0074,0.9755,0.0003</t>
+  </si>
+  <si>
+    <t>0.9612,0.0015,0.0212,0.0002</t>
+  </si>
+  <si>
+    <t>0.9146,0.0036,0.0400,0.0014</t>
+  </si>
+  <si>
+    <t>0.0195,0.0003,0.9847,0.0007</t>
+  </si>
+  <si>
+    <t>0.0101,0.9929,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9991,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7005,0.5000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3032,0.8084,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0227,0.9864,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8387,0.0032,0.1311,0.0005</t>
+  </si>
+  <si>
+    <t>0.9902,0.0001,0.0064,0.0000</t>
+  </si>
+  <si>
+    <t>0.9863,0.0024,0.0008,0.0023</t>
+  </si>
+  <si>
+    <t>0.1701,0.0128,0.7068,0.0029</t>
+  </si>
+  <si>
+    <t>0.9228,0.0010,0.0441,0.0012</t>
+  </si>
+  <si>
+    <t>0.0054,0.0015,0.9873,0.0051</t>
+  </si>
+  <si>
+    <t>0.0111,0.0282,0.9460,0.0014</t>
+  </si>
+  <si>
+    <t>0.0914,0.0619,0.7128,0.0011</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.3414,0.9853,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0016,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0059,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9926,0.0066,0.0006,0.0003</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9512,0.0010,0.0311,0.0001</t>
-  </si>
-  <si>
-    <t>0.0058,0.0004,0.9936,0.0005</t>
-  </si>
-  <si>
-    <t>0.0091,0.0004,0.9921,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0006,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.4221,0.0008,0.6694,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.9969,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.0226,0.9760,0.0082,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.9979,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5359,0.0014,0.3556,0.0033</t>
-  </si>
-  <si>
-    <t>0.0217,0.0074,0.9491,0.0012</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9989,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0393,0.0006,0.9694,0.0002</t>
-  </si>
-  <si>
-    <t>0.0062,0.0000,0.9961,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0022</t>
-  </si>
-  <si>
-    <t>0.0060,0.9940,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.8638,0.0620,0.0144,0.0031</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9998,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.9976,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.5138,0.0014,0.4061,0.0003</t>
-  </si>
-  <si>
-    <t>0.5983,0.4728,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.9962,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.4555,0.7995,0.0016</t>
-  </si>
-  <si>
-    <t>0.0083,0.0016,0.9779,0.0031</t>
-  </si>
-  <si>
-    <t>0.0002,0.0019,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0001,0.9956,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.9709,0.9647,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9992,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9845,0.0002,0.9284</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.6466,0.9664,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9928,0.0033,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9959,0.0031,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0145,0.9948,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0050,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0030,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9927,0.8836,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0012,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9990,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9924,0.0002,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.7136,0.0016,0.3233,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0066,0.9983,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9871,0.9175,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0293,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.6002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0076,0.0001,0.0501,0.9692</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.0021,0.9988</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0095,0.9984</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9969,0.0679,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9902,0.9916,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9602,0.9829,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9821,0.8975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.6600,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.1520,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9934,0.0088,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0064,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.0020,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0110,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.9816,0.0007,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0187,0.9861,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9980,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.1760,0.8512,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.7447,0.0646,0.0436,0.0008</t>
-  </si>
-  <si>
-    <t>0.9755,0.0024,0.0090,0.0001</t>
-  </si>
-  <si>
-    <t>0.0125,0.5833,0.1113,0.0033</t>
-  </si>
-  <si>
-    <t>0.1800,0.0034,0.7380,0.0028</t>
-  </si>
-  <si>
-    <t>0.0055,0.5866,0.0049,0.7911</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9868,0.9642,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.5269,0.5464,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.7804,0.2404,0.0048,0.0015</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0009,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.9139,0.9690,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9799,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0708,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0372,0.9922,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3077,0.0008,0.6290,0.0038</t>
-  </si>
-  <si>
-    <t>0.0088,0.0007,0.9944,0.0003</t>
-  </si>
-  <si>
-    <t>0.9139,0.0053,0.0304,0.0018</t>
-  </si>
-  <si>
-    <t>0.0179,0.0002,0.0003,0.9936</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9892,0.0000</t>
-  </si>
-  <si>
-    <t>0.0451,0.9568,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.0952,0.9386,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.5866,0.0001,0.0020,0.4230</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0046,0.9957,0.0020</t>
-  </si>
-  <si>
-    <t>0.9978,0.0000,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9863,0.0135,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0010,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9832,0.0098,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.8768,0.1223,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9326,0.0168,0.0132,0.0015</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9963,0.0052,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9579,0.0478,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.7519,0.3694,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0174,0.1295,0.9676,0.0005</t>
-  </si>
-  <si>
-    <t>0.9898,0.0143,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0046,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9103,0.0712,0.0135,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0337,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9804,0.0121,0.0034,0.0021</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0069,0.9977,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.0001,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0036,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0067,0.0011,0.9891,0.0011</t>
-  </si>
-  <si>
-    <t>0.0182,0.0010,0.9885,0.0002</t>
-  </si>
-  <si>
-    <t>0.1430,0.0028,0.8815,0.0015</t>
-  </si>
-  <si>
-    <t>0.0125,0.8682,0.0945,0.0001</t>
-  </si>
-  <si>
-    <t>0.0071,0.2398,0.8141,0.0003</t>
-  </si>
-  <si>
-    <t>0.0443,0.0081,0.9175,0.0010</t>
-  </si>
-  <si>
-    <t>0.9644,0.0105,0.0037,0.0007</t>
-  </si>
-  <si>
-    <t>0.0349,0.0009,0.9715,0.0006</t>
-  </si>
-  <si>
-    <t>0.0152,0.9901,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7290,0.4360,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.3400,0.7460,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9800,0.0026,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.9920,0.0001,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.9874,0.0010,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.8703,0.0081,0.0715,0.0023</t>
-  </si>
-  <si>
-    <t>0.9658,0.0031,0.0117,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0004,0.9967,0.0049</t>
-  </si>
-  <si>
-    <t>0.0005,0.0042,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0300,0.9936,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.0006,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.1323,0.9796,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0025,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.1999,0.9936,0.0002</t>
-  </si>
-  <si>
-    <t>0.1571,0.2027,0.3640,0.0025</t>
-  </si>
-  <si>
-    <t>0.9873,0.0007,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.0005,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.7374,0.9779,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0099,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.0081,0.9944,0.0012</t>
-  </si>
-  <si>
-    <t>0.9895,0.0010,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9274,0.0000,0.0990,0.0001</t>
-  </si>
-  <si>
-    <t>0.9866,0.0002,0.0069,0.0003</t>
-  </si>
-  <si>
-    <t>0.9929,0.0072,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0022,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0028,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0920,0.9961,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0015,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.4293,0.8177,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0211,0.0007,0.9668,0.0039</t>
-  </si>
-  <si>
-    <t>0.0082,0.0036,0.9833,0.0006</t>
-  </si>
-  <si>
-    <t>0.0103,0.0034,0.9746,0.0019</t>
-  </si>
-  <si>
-    <t>0.4987,0.0001,0.0010,0.5794</t>
-  </si>
-  <si>
-    <t>0.0132,0.0538,0.0000,0.9671</t>
-  </si>
-  <si>
-    <t>0.0120,0.0012,0.0001,0.9953</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0000,0.0003</t>
+    <t>0.0002,0.0582,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.2103,0.6646,0.0648,0.0010</t>
+  </si>
+  <si>
+    <t>0.9733,0.0005,0.0110,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9977,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.0028,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9167,0.8741,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0128,0.0009,0.9869,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0013,0.9917,0.0029</t>
+  </si>
+  <si>
+    <t>0.0049,0.0045,0.9837,0.0024</t>
+  </si>
+  <si>
+    <t>0.9330,0.0012,0.0417,0.0004</t>
+  </si>
+  <si>
+    <t>0.9612,0.0001,0.0350,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0014,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0071,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.1501,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0047,0.9929,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0090,0.0017,0.9784,0.0101</t>
+  </si>
+  <si>
+    <t>0.0131,0.0033,0.9734,0.0008</t>
+  </si>
+  <si>
+    <t>0.0030,0.0034,0.9741,0.0069</t>
+  </si>
+  <si>
+    <t>0.9389,0.0017,0.0008,0.0237</t>
+  </si>
+  <si>
+    <t>0.0380,0.0490,0.0001,0.9371</t>
+  </si>
+  <si>
+    <t>0.0113,0.0001,0.0006,0.9949</t>
+  </si>
+  <si>
+    <t>0.9940,0.0005,0.0001,0.0032</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1881,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1877,7 +1895,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1891,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1905,7 +1923,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1919,7 +1937,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1933,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1947,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1975,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1989,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2003,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2031,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2045,7 +2063,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2059,7 +2077,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2073,7 +2091,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2084,10 +2102,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2101,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2115,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2129,7 +2147,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2143,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2157,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2171,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,7 +2203,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2199,7 +2217,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2213,7 +2231,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2227,7 +2245,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2238,10 +2256,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2255,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,7 +2287,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,7 +2301,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2297,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2311,7 +2329,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2325,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2336,10 +2354,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2353,7 +2371,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2367,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2378,10 +2396,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2395,7 +2413,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2409,7 +2427,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2420,10 +2438,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2434,10 +2452,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2451,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2465,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2476,10 +2494,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2493,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2507,7 +2525,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2521,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2535,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2546,10 +2564,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2563,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2577,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2591,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2605,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2619,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2633,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2647,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2661,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2675,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2689,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2703,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2717,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2731,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2745,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2759,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2773,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2787,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2801,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2815,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2829,7 +2847,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2843,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2857,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2871,7 +2889,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2885,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2896,10 +2914,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2913,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2927,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2941,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2955,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2969,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2983,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2997,7 +3015,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3011,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3025,7 +3043,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3039,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3053,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3067,7 +3085,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3081,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3095,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3109,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3123,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3137,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3151,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3165,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3179,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3193,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3207,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3235,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3249,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3263,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3277,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>350</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3305,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3319,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3333,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3347,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3361,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3375,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3389,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3403,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3417,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>362</v>
+        <v>282</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3431,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3445,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3456,10 +3474,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3473,7 +3491,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3484,10 +3502,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,7 +3519,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3512,10 +3530,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3529,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3543,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3557,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3571,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3585,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3599,7 +3617,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3610,10 +3628,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3627,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3641,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>271</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3655,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3669,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3683,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3697,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>323</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3711,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3725,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3739,7 +3757,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3753,7 +3771,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3767,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3781,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3795,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3806,10 +3824,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3823,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3837,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3848,10 +3866,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3865,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3879,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3893,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3907,7 +3925,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3921,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3935,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3949,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3963,7 +3981,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3977,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3988,10 +4006,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4005,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4019,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4033,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4047,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4058,10 +4076,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4075,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4089,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4100,10 +4118,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4117,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4131,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4145,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4159,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>408</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4173,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4187,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4201,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4215,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4229,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4243,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4254,10 +4272,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4271,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4282,10 +4300,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4296,10 +4314,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4313,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4327,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4341,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4355,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4369,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4383,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4397,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4411,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4425,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4439,7 +4457,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4453,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4467,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4481,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4495,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4509,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4523,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4534,10 +4552,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4551,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4562,10 +4580,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4579,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4593,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4607,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4621,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4632,10 +4650,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4649,7 +4667,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4663,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4677,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4691,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4705,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4716,10 +4734,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4747,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4761,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4775,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4789,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4803,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4817,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4831,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>453</v>
+        <v>384</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4845,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4859,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4873,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4887,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4901,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>457</v>
+        <v>401</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4915,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>271</v>
+        <v>462</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4929,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4940,10 +4958,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4957,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4971,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4985,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4999,7 +5017,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5013,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5027,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5041,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5055,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5069,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5083,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5097,7 +5115,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5111,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>384</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5125,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5139,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>320</v>
+        <v>477</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5153,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>270</v>
+        <v>323</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5167,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5181,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5195,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>270</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5209,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5223,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5237,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5251,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5265,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5279,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5293,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5307,7 +5325,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5321,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5335,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5346,10 +5364,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5363,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5377,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5391,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5405,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5419,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
